--- a/META Model.xlsx
+++ b/META Model.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kerem\OneDrive\Masaüstü\Models\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fe4885f5b5840770/Masaüstü/Financial Models/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A02D53C4-B977-4F18-8B1E-4D8C901C82EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13704" yWindow="0" windowWidth="33252" windowHeight="16344" xr2:uid="{64BEE0EA-45A1-4490-9445-11F5F6D37C44}"/>
+    <workbookView xWindow="32784" yWindow="1692" windowWidth="25872" windowHeight="13368" xr2:uid="{64BEE0EA-45A1-4490-9445-11F5F6D37C44}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -2452,7 +2452,7 @@
         <v>0.30068515801880791</v>
       </c>
       <c r="F46" s="10">
-        <f t="shared" ref="F46:N46" si="17">F45/F36</f>
+        <f t="shared" ref="F46:L46" si="17">F45/F36</f>
         <v>0.2322119218928213</v>
       </c>
       <c r="G46" s="10">
